--- a/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
+++ b/в бланки заводов/Останкино СЫР/OrderCheeseInForm/lib/DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CBADD7-8867-47FB-AC50-9B7986D97D77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AF5C2D-113E-42A6-BE85-2F1C3CB899E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="124">
   <si>
     <t>SKU</t>
   </si>
@@ -400,6 +400,12 @@
   </si>
   <si>
     <t>Продукт По-Российски Классический с заменителем молочного жира мдж 50% ТМ Коровино</t>
+  </si>
+  <si>
+    <t>Майонез провансаль классический с массовой долей жира 67% ТМ «ПАПА МОЖЕТ» 186г дой-пак с дозатором</t>
+  </si>
+  <si>
+    <t>Майонез провансаль классический оливковый с массовой долей жира 67% ТМ «ПАПА МОЖЕТ» 186г дой-пак с дозатором</t>
   </si>
 </sst>
 </file>
@@ -748,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -1563,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="b">
-        <f t="shared" ref="G34:G59" si="1">COUNTIF(B:B,B34)&gt;1</f>
+        <f t="shared" ref="G34:G61" si="1">COUNTIF(B:B,B34)&gt;1</f>
         <v>1</v>
       </c>
     </row>
@@ -2163,6 +2169,54 @@
         <v>1</v>
       </c>
       <c r="G59" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60">
+        <v>6948362</v>
+      </c>
+      <c r="C60" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60">
+        <v>0.186</v>
+      </c>
+      <c r="G60" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61">
+        <v>6948508</v>
+      </c>
+      <c r="C61" t="s">
+        <v>123</v>
+      </c>
+      <c r="D61">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61">
+        <v>0.186</v>
+      </c>
+      <c r="G61" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
